--- a/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
+++ b/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A08177-B56A-43FE-A2F2-ADE30AA352B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B992F9-CDFF-4A23-8EA4-96C497E6C6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListRelacion impactos-indicador" sheetId="3" r:id="rId1"/>

--- a/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
+++ b/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B992F9-CDFF-4A23-8EA4-96C497E6C6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BA24E1-C52A-42F2-B5DD-0313D4EF765E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListRelacion impactos-indicador" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Compuestos" sheetId="16" r:id="rId7"/>
     <sheet name="Corriente" sheetId="5" r:id="rId8"/>
     <sheet name="Francobordo" sheetId="9" r:id="rId9"/>
-    <sheet name="Inundación" sheetId="10" r:id="rId10"/>
+    <sheet name="Inundación costera" sheetId="10" r:id="rId10"/>
     <sheet name="Precipitación" sheetId="7" r:id="rId11"/>
     <sheet name="Rebase" sheetId="15" r:id="rId12"/>
     <sheet name="Temperatura" sheetId="13" r:id="rId13"/>
@@ -33,13 +33,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agitación-Oleaje'!$A$1:$P$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Asociados!$B$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CONTAR!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ListRelacion impactos-indicador'!$A$1:$F$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ListRelacion impactos-indicador'!$A$1:$P$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Temperatura!$B$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Viento!$A$1:$P$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Agitación-Oleaje'!$A$1:$P$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Compuestos!$A$1:$P$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">Corriente!$A$1:$P$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">Inundación!$A$1:$P$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Inundación costera'!$A$1:$P$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'ListRelacion impactos-indicador'!$A$1:$P$182</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">Precipitación!$A$1:$P$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">Rebase!$A$1:$P$5</definedName>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="135">
   <si>
     <t>Nº</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>Dársenas (zona de permanencia)</t>
+  </si>
+  <si>
+    <t>Inundación pluvial</t>
   </si>
 </sst>
 </file>
@@ -954,6 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1025,7 +1029,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -1064,7 +1068,7 @@
       </c>
       <c r="P2" s="17"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -1099,7 +1103,7 @@
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -1134,7 +1138,7 @@
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>4</v>
       </c>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="P5" s="17"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -1212,7 +1216,7 @@
       </c>
       <c r="P6" s="17"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>6</v>
       </c>
@@ -1247,7 +1251,7 @@
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>7</v>
       </c>
@@ -1282,7 +1286,7 @@
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>8</v>
       </c>
@@ -1317,7 +1321,7 @@
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>9</v>
       </c>
@@ -1352,7 +1356,7 @@
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>10</v>
       </c>
@@ -1387,7 +1391,7 @@
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>11</v>
       </c>
@@ -1422,7 +1426,7 @@
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>12</v>
       </c>
@@ -1457,7 +1461,7 @@
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>13</v>
       </c>
@@ -1492,7 +1496,7 @@
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>14</v>
       </c>
@@ -1527,7 +1531,7 @@
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>15</v>
       </c>
@@ -1562,7 +1566,7 @@
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>16</v>
       </c>
@@ -1597,7 +1601,7 @@
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>17</v>
       </c>
@@ -1632,7 +1636,7 @@
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>18</v>
       </c>
@@ -1667,7 +1671,7 @@
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>19</v>
       </c>
@@ -1702,7 +1706,7 @@
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>20</v>
       </c>
@@ -1737,7 +1741,7 @@
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>21</v>
       </c>
@@ -1772,7 +1776,7 @@
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>22</v>
       </c>
@@ -1807,7 +1811,7 @@
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>23</v>
       </c>
@@ -1842,7 +1846,7 @@
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>24</v>
       </c>
@@ -1877,7 +1881,7 @@
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>25</v>
       </c>
@@ -1912,7 +1916,7 @@
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>26</v>
       </c>
@@ -1947,7 +1951,7 @@
       <c r="O27" s="17"/>
       <c r="P27" s="17"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>27</v>
       </c>
@@ -1982,7 +1986,7 @@
       <c r="O28" s="17"/>
       <c r="P28" s="17"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <v>28</v>
       </c>
@@ -2015,7 +2019,7 @@
       <c r="O29" s="17"/>
       <c r="P29" s="17"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <v>29</v>
       </c>
@@ -2048,7 +2052,7 @@
       <c r="O30" s="17"/>
       <c r="P30" s="17"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <v>30</v>
       </c>
@@ -2081,7 +2085,7 @@
       <c r="O31" s="17"/>
       <c r="P31" s="17"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <v>31</v>
       </c>
@@ -2114,7 +2118,7 @@
       <c r="O32" s="17"/>
       <c r="P32" s="17"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <v>32</v>
       </c>
@@ -2147,7 +2151,7 @@
       <c r="O33" s="17"/>
       <c r="P33" s="17"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <v>33</v>
       </c>
@@ -2180,7 +2184,7 @@
       <c r="O34" s="17"/>
       <c r="P34" s="17"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <v>34</v>
       </c>
@@ -2213,7 +2217,7 @@
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <v>35</v>
       </c>
@@ -2246,7 +2250,7 @@
       <c r="O36" s="17"/>
       <c r="P36" s="17"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <v>36</v>
       </c>
@@ -2281,7 +2285,7 @@
       <c r="O37" s="17"/>
       <c r="P37" s="17"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <v>37</v>
       </c>
@@ -2328,7 +2332,7 @@
       </c>
       <c r="P38" s="17"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <v>38</v>
       </c>
@@ -2363,7 +2367,7 @@
       <c r="O39" s="17"/>
       <c r="P39" s="17"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <v>39</v>
       </c>
@@ -2398,7 +2402,7 @@
       <c r="O40" s="17"/>
       <c r="P40" s="17"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <v>40</v>
       </c>
@@ -2445,7 +2449,7 @@
       </c>
       <c r="P41" s="17"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <v>41</v>
       </c>
@@ -2480,7 +2484,7 @@
       <c r="O42" s="17"/>
       <c r="P42" s="17"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <v>42</v>
       </c>
@@ -2515,7 +2519,7 @@
       <c r="O43" s="17"/>
       <c r="P43" s="17"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <v>43</v>
       </c>
@@ -2562,7 +2566,7 @@
       </c>
       <c r="P44" s="17"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <v>44</v>
       </c>
@@ -2597,7 +2601,7 @@
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <v>45</v>
       </c>
@@ -2644,7 +2648,7 @@
       </c>
       <c r="P46" s="17"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <v>46</v>
       </c>
@@ -2679,7 +2683,7 @@
       <c r="O47" s="17"/>
       <c r="P47" s="17"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <v>47</v>
       </c>
@@ -2714,7 +2718,7 @@
       <c r="O48" s="17"/>
       <c r="P48" s="17"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="17">
         <v>48</v>
       </c>
@@ -2761,7 +2765,7 @@
       </c>
       <c r="P49" s="17"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="17">
         <v>49</v>
       </c>
@@ -2796,7 +2800,7 @@
       <c r="O50" s="17"/>
       <c r="P50" s="17"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <v>50</v>
       </c>
@@ -2837,7 +2841,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>44</v>
@@ -2850,7 +2854,7 @@
       </c>
       <c r="G52" s="17" t="str">
         <f>IF(C52="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C52,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C52,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H52" s="17"/>
       <c r="I52" s="17"/>
@@ -2870,7 +2874,7 @@
         <v>6</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D53" s="17" t="s">
         <v>44</v>
@@ -2883,7 +2887,7 @@
       </c>
       <c r="G53" s="17" t="str">
         <f>IF(C53="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C53,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C53,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H53" s="17"/>
       <c r="I53" s="17"/>
@@ -2895,7 +2899,7 @@
       <c r="O53" s="17"/>
       <c r="P53" s="17"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17">
         <v>53</v>
       </c>
@@ -2936,7 +2940,7 @@
         <v>6</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>44</v>
@@ -2949,7 +2953,7 @@
       </c>
       <c r="G55" s="17" t="str">
         <f>IF(C55="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C55,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C55,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="17"/>
@@ -2961,7 +2965,7 @@
       <c r="O55" s="17"/>
       <c r="P55" s="17"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="17">
         <v>55</v>
       </c>
@@ -2994,7 +2998,7 @@
       <c r="O56" s="17"/>
       <c r="P56" s="17"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
         <v>56</v>
       </c>
@@ -3005,7 +3009,7 @@
         <v>43</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>50</v>
@@ -3027,7 +3031,7 @@
       <c r="O57" s="17"/>
       <c r="P57" s="17"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="17">
         <v>57</v>
       </c>
@@ -3068,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>44</v>
@@ -3081,7 +3085,7 @@
       </c>
       <c r="G59" s="17" t="str">
         <f>IF(C59="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C59,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C59,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
@@ -3101,7 +3105,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D60" s="17" t="s">
         <v>44</v>
@@ -3114,7 +3118,7 @@
       </c>
       <c r="G60" s="17" t="str">
         <f>IF(C60="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C60,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C60,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -3134,7 +3138,7 @@
         <v>6</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>44</v>
@@ -3147,7 +3151,7 @@
       </c>
       <c r="G61" s="17" t="str">
         <f>IF(C61="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C61,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C61,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
@@ -3159,7 +3163,7 @@
       <c r="O61" s="17"/>
       <c r="P61" s="17"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="17">
         <v>61</v>
       </c>
@@ -3200,7 +3204,7 @@
         <v>6</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D63" s="17" t="s">
         <v>44</v>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="G63" s="17" t="str">
         <f>IF(C63="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C63,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C63,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="17"/>
@@ -3225,7 +3229,7 @@
       <c r="O63" s="17"/>
       <c r="P63" s="17"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <v>63</v>
       </c>
@@ -3258,7 +3262,7 @@
       <c r="O64" s="17"/>
       <c r="P64" s="17"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <v>64</v>
       </c>
@@ -3291,7 +3295,7 @@
       <c r="O65" s="17"/>
       <c r="P65" s="17"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17">
         <v>65</v>
       </c>
@@ -3324,7 +3328,7 @@
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <v>66</v>
       </c>
@@ -3357,7 +3361,7 @@
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17">
         <v>67</v>
       </c>
@@ -3398,7 +3402,7 @@
         <v>6</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D69" s="17" t="s">
         <v>44</v>
@@ -3411,7 +3415,7 @@
       </c>
       <c r="G69" s="17" t="str">
         <f>IF(C69="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C69,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C69,UnidadMedida!$A$1:$A$30,0))),""))</f>
-        <v>m</v>
+        <v/>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="17"/>
@@ -3423,7 +3427,7 @@
       <c r="O69" s="17"/>
       <c r="P69" s="17"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="17">
         <v>69</v>
       </c>
@@ -3456,7 +3460,7 @@
       <c r="O70" s="17"/>
       <c r="P70" s="17"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17">
         <v>70</v>
       </c>
@@ -3489,7 +3493,7 @@
       <c r="O71" s="17"/>
       <c r="P71" s="17"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="17">
         <v>71</v>
       </c>
@@ -3522,7 +3526,7 @@
       <c r="O72" s="17"/>
       <c r="P72" s="17"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17">
         <v>72</v>
       </c>
@@ -3555,7 +3559,7 @@
       <c r="O73" s="17"/>
       <c r="P73" s="17"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="17">
         <v>73</v>
       </c>
@@ -3588,7 +3592,7 @@
       <c r="O74" s="17"/>
       <c r="P74" s="17"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17">
         <v>74</v>
       </c>
@@ -3621,7 +3625,7 @@
       <c r="O75" s="17"/>
       <c r="P75" s="17"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="17">
         <v>75</v>
       </c>
@@ -3654,7 +3658,7 @@
       <c r="O76" s="17"/>
       <c r="P76" s="17"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17">
         <v>76</v>
       </c>
@@ -3687,7 +3691,7 @@
       <c r="O77" s="17"/>
       <c r="P77" s="17"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17">
         <v>77</v>
       </c>
@@ -3720,7 +3724,7 @@
       <c r="O78" s="17"/>
       <c r="P78" s="17"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17">
         <v>78</v>
       </c>
@@ -3753,7 +3757,7 @@
       <c r="O79" s="17"/>
       <c r="P79" s="17"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17">
         <v>79</v>
       </c>
@@ -3786,7 +3790,7 @@
       <c r="O80" s="17"/>
       <c r="P80" s="17"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17">
         <v>80</v>
       </c>
@@ -3819,7 +3823,7 @@
       <c r="O81" s="17"/>
       <c r="P81" s="17"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17">
         <v>81</v>
       </c>
@@ -3852,7 +3856,7 @@
       <c r="O82" s="17"/>
       <c r="P82" s="17"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17">
         <v>82</v>
       </c>
@@ -3885,7 +3889,7 @@
       <c r="O83" s="17"/>
       <c r="P83" s="17"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="17">
         <v>83</v>
       </c>
@@ -3918,7 +3922,7 @@
       <c r="O84" s="17"/>
       <c r="P84" s="17"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17">
         <v>84</v>
       </c>
@@ -3951,7 +3955,7 @@
       <c r="O85" s="17"/>
       <c r="P85" s="17"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17">
         <v>85</v>
       </c>
@@ -3984,7 +3988,7 @@
       <c r="O86" s="17"/>
       <c r="P86" s="17"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17">
         <v>86</v>
       </c>
@@ -4017,7 +4021,7 @@
       <c r="O87" s="17"/>
       <c r="P87" s="17"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17">
         <v>87</v>
       </c>
@@ -4050,7 +4054,7 @@
       <c r="O88" s="17"/>
       <c r="P88" s="17"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17">
         <v>88</v>
       </c>
@@ -4083,7 +4087,7 @@
       <c r="O89" s="17"/>
       <c r="P89" s="17"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17">
         <v>89</v>
       </c>
@@ -4116,7 +4120,7 @@
       <c r="O90" s="17"/>
       <c r="P90" s="17"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17">
         <v>90</v>
       </c>
@@ -4149,7 +4153,7 @@
       <c r="O91" s="17"/>
       <c r="P91" s="17"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17">
         <v>91</v>
       </c>
@@ -4182,7 +4186,7 @@
       <c r="O92" s="17"/>
       <c r="P92" s="17"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17">
         <v>92</v>
       </c>
@@ -4215,7 +4219,7 @@
       <c r="O93" s="17"/>
       <c r="P93" s="17"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17">
         <v>93</v>
       </c>
@@ -4248,7 +4252,7 @@
       <c r="O94" s="17"/>
       <c r="P94" s="17"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17">
         <v>94</v>
       </c>
@@ -4283,7 +4287,7 @@
       <c r="O95" s="17"/>
       <c r="P95" s="17"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="17">
         <v>95</v>
       </c>
@@ -4318,7 +4322,7 @@
       <c r="O96" s="17"/>
       <c r="P96" s="17"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17">
         <v>96</v>
       </c>
@@ -4353,7 +4357,7 @@
       <c r="O97" s="17"/>
       <c r="P97" s="17"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17">
         <v>97</v>
       </c>
@@ -4388,7 +4392,7 @@
       <c r="O98" s="17"/>
       <c r="P98" s="17"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17">
         <v>98</v>
       </c>
@@ -4423,7 +4427,7 @@
       <c r="O99" s="17"/>
       <c r="P99" s="17"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17">
         <v>99</v>
       </c>
@@ -4456,7 +4460,7 @@
       <c r="O100" s="17"/>
       <c r="P100" s="17"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17">
         <v>100</v>
       </c>
@@ -4489,7 +4493,7 @@
       <c r="O101" s="17"/>
       <c r="P101" s="17"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="17">
         <v>101</v>
       </c>
@@ -4522,7 +4526,7 @@
       <c r="O102" s="17"/>
       <c r="P102" s="17"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17">
         <v>102</v>
       </c>
@@ -4555,7 +4559,7 @@
       <c r="O103" s="17"/>
       <c r="P103" s="17"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17">
         <v>103</v>
       </c>
@@ -4588,7 +4592,7 @@
       <c r="O104" s="17"/>
       <c r="P104" s="17"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17">
         <v>104</v>
       </c>
@@ -4621,7 +4625,7 @@
       <c r="O105" s="17"/>
       <c r="P105" s="17"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="17">
         <v>105</v>
       </c>
@@ -4654,7 +4658,7 @@
       <c r="O106" s="17"/>
       <c r="P106" s="17"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17">
         <v>106</v>
       </c>
@@ -4687,7 +4691,7 @@
       <c r="O107" s="17"/>
       <c r="P107" s="17"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="17">
         <v>107</v>
       </c>
@@ -4720,7 +4724,7 @@
       <c r="O108" s="17"/>
       <c r="P108" s="17"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17">
         <v>108</v>
       </c>
@@ -4753,7 +4757,7 @@
       <c r="O109" s="17"/>
       <c r="P109" s="17"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="17">
         <v>109</v>
       </c>
@@ -4786,7 +4790,7 @@
       <c r="O110" s="17"/>
       <c r="P110" s="17"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17">
         <v>110</v>
       </c>
@@ -4819,7 +4823,7 @@
       <c r="O111" s="17"/>
       <c r="P111" s="17"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="17">
         <v>111</v>
       </c>
@@ -4852,7 +4856,7 @@
       <c r="O112" s="17"/>
       <c r="P112" s="17"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17">
         <v>112</v>
       </c>
@@ -4885,7 +4889,7 @@
       <c r="O113" s="17"/>
       <c r="P113" s="17"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="17">
         <v>113</v>
       </c>
@@ -4918,7 +4922,7 @@
       <c r="O114" s="17"/>
       <c r="P114" s="17"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17">
         <v>114</v>
       </c>
@@ -4951,7 +4955,7 @@
       <c r="O115" s="17"/>
       <c r="P115" s="17"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="17">
         <v>115</v>
       </c>
@@ -4984,7 +4988,7 @@
       <c r="O116" s="17"/>
       <c r="P116" s="17"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17">
         <v>116</v>
       </c>
@@ -5017,7 +5021,7 @@
       <c r="O117" s="17"/>
       <c r="P117" s="17"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="17">
         <v>117</v>
       </c>
@@ -5050,7 +5054,7 @@
       <c r="O118" s="17"/>
       <c r="P118" s="17"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17">
         <v>118</v>
       </c>
@@ -5083,7 +5087,7 @@
       <c r="O119" s="17"/>
       <c r="P119" s="17"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="17">
         <v>119</v>
       </c>
@@ -5116,7 +5120,7 @@
       <c r="O120" s="17"/>
       <c r="P120" s="17"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17">
         <v>120</v>
       </c>
@@ -5149,7 +5153,7 @@
       <c r="O121" s="17"/>
       <c r="P121" s="17"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="17">
         <v>121</v>
       </c>
@@ -5182,7 +5186,7 @@
       <c r="O122" s="17"/>
       <c r="P122" s="17"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17">
         <v>122</v>
       </c>
@@ -5215,7 +5219,7 @@
       <c r="O123" s="17"/>
       <c r="P123" s="17"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="17">
         <v>123</v>
       </c>
@@ -5248,7 +5252,7 @@
       <c r="O124" s="17"/>
       <c r="P124" s="17"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17">
         <v>124</v>
       </c>
@@ -5281,7 +5285,7 @@
       <c r="O125" s="17"/>
       <c r="P125" s="17"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="17">
         <v>125</v>
       </c>
@@ -5314,7 +5318,7 @@
       <c r="O126" s="17"/>
       <c r="P126" s="17"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17">
         <v>126</v>
       </c>
@@ -5347,7 +5351,7 @@
       <c r="O127" s="17"/>
       <c r="P127" s="17"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="17">
         <v>127</v>
       </c>
@@ -5380,7 +5384,7 @@
       <c r="O128" s="17"/>
       <c r="P128" s="17"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17">
         <v>128</v>
       </c>
@@ -5413,7 +5417,7 @@
       <c r="O129" s="17"/>
       <c r="P129" s="17"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="17">
         <v>129</v>
       </c>
@@ -5446,7 +5450,7 @@
       <c r="O130" s="17"/>
       <c r="P130" s="17"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17">
         <v>130</v>
       </c>
@@ -5479,7 +5483,7 @@
       <c r="O131" s="17"/>
       <c r="P131" s="17"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="17">
         <v>131</v>
       </c>
@@ -5512,7 +5516,7 @@
       <c r="O132" s="17"/>
       <c r="P132" s="17"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17">
         <v>132</v>
       </c>
@@ -5545,7 +5549,7 @@
       <c r="O133" s="17"/>
       <c r="P133" s="17"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="17">
         <v>133</v>
       </c>
@@ -5578,7 +5582,7 @@
       <c r="O134" s="17"/>
       <c r="P134" s="17"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17">
         <v>134</v>
       </c>
@@ -5611,7 +5615,7 @@
       <c r="O135" s="17"/>
       <c r="P135" s="17"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="17">
         <v>135</v>
       </c>
@@ -5644,7 +5648,7 @@
       <c r="O136" s="17"/>
       <c r="P136" s="17"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17">
         <v>136</v>
       </c>
@@ -5677,7 +5681,7 @@
       <c r="O137" s="17"/>
       <c r="P137" s="17"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="17">
         <v>137</v>
       </c>
@@ -5710,7 +5714,7 @@
       <c r="O138" s="17"/>
       <c r="P138" s="17"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17">
         <v>138</v>
       </c>
@@ -5743,7 +5747,7 @@
       <c r="O139" s="17"/>
       <c r="P139" s="17"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="17">
         <v>139</v>
       </c>
@@ -5776,7 +5780,7 @@
       <c r="O140" s="17"/>
       <c r="P140" s="17"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17">
         <v>140</v>
       </c>
@@ -5809,7 +5813,7 @@
       <c r="O141" s="17"/>
       <c r="P141" s="17"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="17">
         <v>141</v>
       </c>
@@ -5842,7 +5846,7 @@
       <c r="O142" s="17"/>
       <c r="P142" s="17"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17">
         <v>142</v>
       </c>
@@ -5875,7 +5879,7 @@
       <c r="O143" s="17"/>
       <c r="P143" s="17"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="17">
         <v>143</v>
       </c>
@@ -5908,7 +5912,7 @@
       <c r="O144" s="17"/>
       <c r="P144" s="17"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17">
         <v>144</v>
       </c>
@@ -5941,7 +5945,7 @@
       <c r="O145" s="17"/>
       <c r="P145" s="17"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="17">
         <v>145</v>
       </c>
@@ -5974,7 +5978,7 @@
       <c r="O146" s="17"/>
       <c r="P146" s="17"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17">
         <v>146</v>
       </c>
@@ -6007,7 +6011,7 @@
       <c r="O147" s="17"/>
       <c r="P147" s="17"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="17">
         <v>147</v>
       </c>
@@ -6040,7 +6044,7 @@
       <c r="O148" s="17"/>
       <c r="P148" s="17"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17">
         <v>148</v>
       </c>
@@ -6073,7 +6077,7 @@
       <c r="O149" s="17"/>
       <c r="P149" s="17"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17">
         <v>149</v>
       </c>
@@ -6106,7 +6110,7 @@
       <c r="O150" s="17"/>
       <c r="P150" s="17"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17">
         <v>150</v>
       </c>
@@ -6139,7 +6143,7 @@
       <c r="O151" s="17"/>
       <c r="P151" s="17"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="17">
         <v>151</v>
       </c>
@@ -6172,7 +6176,7 @@
       <c r="O152" s="17"/>
       <c r="P152" s="17"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17">
         <v>152</v>
       </c>
@@ -6207,7 +6211,7 @@
       <c r="O153" s="17"/>
       <c r="P153" s="17"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="17">
         <v>153</v>
       </c>
@@ -6242,7 +6246,7 @@
       <c r="O154" s="17"/>
       <c r="P154" s="17"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17">
         <v>154</v>
       </c>
@@ -6277,7 +6281,7 @@
       <c r="O155" s="17"/>
       <c r="P155" s="17"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="17">
         <v>155</v>
       </c>
@@ -6312,7 +6316,7 @@
       <c r="O156" s="17"/>
       <c r="P156" s="17"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17">
         <v>156</v>
       </c>
@@ -6347,7 +6351,7 @@
       <c r="O157" s="17"/>
       <c r="P157" s="17"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="17">
         <v>157</v>
       </c>
@@ -6380,7 +6384,7 @@
       <c r="O158" s="17"/>
       <c r="P158" s="17"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17">
         <v>158</v>
       </c>
@@ -6413,7 +6417,7 @@
       <c r="O159" s="17"/>
       <c r="P159" s="17"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="17">
         <v>159</v>
       </c>
@@ -6446,7 +6450,7 @@
       <c r="O160" s="17"/>
       <c r="P160" s="17"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17">
         <v>160</v>
       </c>
@@ -6479,7 +6483,7 @@
       <c r="O161" s="17"/>
       <c r="P161" s="17"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="17">
         <v>161</v>
       </c>
@@ -6512,7 +6516,7 @@
       <c r="O162" s="17"/>
       <c r="P162" s="17"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17">
         <v>162</v>
       </c>
@@ -6545,7 +6549,7 @@
       <c r="O163" s="17"/>
       <c r="P163" s="17"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="17">
         <v>163</v>
       </c>
@@ -6578,7 +6582,7 @@
       <c r="O164" s="17"/>
       <c r="P164" s="17"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17">
         <v>164</v>
       </c>
@@ -6611,7 +6615,7 @@
       <c r="O165" s="17"/>
       <c r="P165" s="17"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="17">
         <v>165</v>
       </c>
@@ -6644,7 +6648,7 @@
       <c r="O166" s="17"/>
       <c r="P166" s="17"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17">
         <v>166</v>
       </c>
@@ -6677,7 +6681,7 @@
       <c r="O167" s="17"/>
       <c r="P167" s="17"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="17">
         <v>167</v>
       </c>
@@ -6710,7 +6714,7 @@
       <c r="O168" s="17"/>
       <c r="P168" s="17"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17">
         <v>168</v>
       </c>
@@ -6743,7 +6747,7 @@
       <c r="O169" s="17"/>
       <c r="P169" s="17"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="17">
         <v>169</v>
       </c>
@@ -6776,7 +6780,7 @@
       <c r="O170" s="17"/>
       <c r="P170" s="17"/>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17">
         <v>170</v>
       </c>
@@ -6809,7 +6813,7 @@
       <c r="O171" s="17"/>
       <c r="P171" s="17"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="17">
         <v>171</v>
       </c>
@@ -6842,7 +6846,7 @@
       <c r="O172" s="17"/>
       <c r="P172" s="17"/>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17">
         <v>172</v>
       </c>
@@ -6875,7 +6879,7 @@
       <c r="O173" s="17"/>
       <c r="P173" s="17"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="17">
         <v>173</v>
       </c>
@@ -6908,7 +6912,7 @@
       <c r="O174" s="17"/>
       <c r="P174" s="17"/>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17">
         <v>174</v>
       </c>
@@ -6941,7 +6945,7 @@
       <c r="O175" s="17"/>
       <c r="P175" s="17"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="17">
         <v>175</v>
       </c>
@@ -6974,7 +6978,7 @@
       <c r="O176" s="17"/>
       <c r="P176" s="17"/>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17">
         <v>176</v>
       </c>
@@ -7007,7 +7011,7 @@
       <c r="O177" s="17"/>
       <c r="P177" s="17"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="17">
         <v>177</v>
       </c>
@@ -7040,7 +7044,7 @@
       <c r="O178" s="17"/>
       <c r="P178" s="17"/>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17">
         <v>178</v>
       </c>
@@ -7073,7 +7077,7 @@
       <c r="O179" s="17"/>
       <c r="P179" s="17"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="17">
         <v>179</v>
       </c>
@@ -7106,7 +7110,7 @@
       <c r="O180" s="17"/>
       <c r="P180" s="17"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17">
         <v>180</v>
       </c>
@@ -7139,7 +7143,7 @@
       <c r="O181" s="17"/>
       <c r="P181" s="17"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="17">
         <v>181</v>
       </c>
@@ -7173,6 +7177,18 @@
       <c r="P182" s="17"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P182" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ELO"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Inundación costera"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="19" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -7222,7 +7238,7 @@
       </c>
       <c r="H1" s="11" t="str">
         <f>+_xlfn.CONCAT('ListRelacion impactos-indicador'!$H$1, " (",'ListRelacion impactos-indicador'!$G$52,")")</f>
-        <v>Umbral General (m)</v>
+        <v>Umbral General ()</v>
       </c>
       <c r="I1" s="12" t="s">
         <v>101</v>
@@ -7251,67 +7267,67 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="str" cm="1">
-        <f t="array" ref="A2:A54">_xlfn._xlws.FILTER(IF(B2:B176&lt;&gt;"","Inundación",""),B2:B176&lt;&gt;"")</f>
+        <f t="array" ref="A2:A53">_xlfn._xlws.FILTER(IF(B2:B176&lt;&gt;"","Inundación",""),B2:B176&lt;&gt;"")</f>
         <v>Inundación</v>
       </c>
       <c r="B2" s="7" cm="1">
-        <f t="array" ref="B2:B54">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!A2:A182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="B2:B53">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!A2:A182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v>51</v>
       </c>
       <c r="C2" s="7" t="str" cm="1">
-        <f t="array" ref="C2:C54">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!B2:B182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="C2:C53">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!B2:B182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v>ELO</v>
       </c>
       <c r="D2" s="7" t="str" cm="1">
-        <f t="array" ref="D2:D54">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!C2:C182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
-        <v>Inundación</v>
+        <f t="array" ref="D2:D53">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!C2:C182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <v>Inundación costera</v>
       </c>
       <c r="E2" s="7" t="str" cm="1">
-        <f t="array" ref="E2:E54">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!D2:D182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="E2:E53">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!D2:D182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v>Inundación costera</v>
       </c>
       <c r="F2" s="7" t="str" cm="1">
-        <f t="array" ref="F2:F54">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!E2:E182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="F2:F53">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!E2:E182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v>Superficies</v>
       </c>
       <c r="G2" s="7" t="str" cm="1">
-        <f t="array" ref="G2:G54">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!F2:F182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="G2:G53">_xlfn._xlws.FILTER('ListRelacion impactos-indicador'!F2:F182,'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v>Activo físico</v>
       </c>
       <c r="H2" s="7" t="str" cm="1">
-        <f t="array" ref="H2:H54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!H2:H182="","",'ListRelacion impactos-indicador'!H2:H182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="H2:H53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!H2:H182="","",'ListRelacion impactos-indicador'!H2:H182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="I2" s="7" t="str" cm="1">
-        <f t="array" ref="I2:I54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!I2:I182="","",'ListRelacion impactos-indicador'!I2:I182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="I2:I53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!I2:I182="","",'ListRelacion impactos-indicador'!I2:I182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="J2" s="7" t="str" cm="1">
-        <f t="array" ref="J2:J54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!J2:J182="","",'ListRelacion impactos-indicador'!J2:J182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="J2:J53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!J2:J182="","",'ListRelacion impactos-indicador'!J2:J182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="K2" s="7" t="str" cm="1">
-        <f t="array" ref="K2:K54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!K2:K182="","",'ListRelacion impactos-indicador'!K2:K182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="K2:K53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!K2:K182="","",'ListRelacion impactos-indicador'!K2:K182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="L2" s="7" t="str" cm="1">
-        <f t="array" ref="L2:L54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!L2:L182="","",'ListRelacion impactos-indicador'!L2:L182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="L2:L53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!L2:L182="","",'ListRelacion impactos-indicador'!L2:L182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="M2" s="7" t="str" cm="1">
-        <f t="array" ref="M2:M54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!M2:M182="","",'ListRelacion impactos-indicador'!M2:M182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="M2:M53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!M2:M182="","",'ListRelacion impactos-indicador'!M2:M182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="N2" s="7" t="str" cm="1">
-        <f t="array" ref="N2:N54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!N2:N182="","",'ListRelacion impactos-indicador'!N2:N182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="N2:N53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!N2:N182="","",'ListRelacion impactos-indicador'!N2:N182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="O2" s="7" t="str" cm="1">
-        <f t="array" ref="O2:O54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!O2:O182="","",'ListRelacion impactos-indicador'!O2:O182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="O2:O53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!O2:O182="","",'ListRelacion impactos-indicador'!O2:O182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
       <c r="P2" s="7" t="str" cm="1">
-        <f t="array" ref="P2:P54">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!P2:P182="","",'ListRelacion impactos-indicador'!P2:P182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
+        <f t="array" ref="P2:P53">_xlfn._xlws.FILTER(IF('ListRelacion impactos-indicador'!P2:P182="","",'ListRelacion impactos-indicador'!P2:P182),'ListRelacion impactos-indicador'!$D$2:$D$182="Inundación costera","")</f>
         <v/>
       </c>
     </row>
@@ -7326,7 +7342,7 @@
         <v>ELO</v>
       </c>
       <c r="D3" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E3" s="7" t="str">
         <v>Inundación costera</v>
@@ -7426,7 +7442,7 @@
         <v>ELO</v>
       </c>
       <c r="D5" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E5" s="7" t="str">
         <v>Inundación costera</v>
@@ -7520,7 +7536,7 @@
         <v>Inundación</v>
       </c>
       <c r="B7" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="7" t="str">
         <v>ELO</v>
@@ -7532,7 +7548,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F7" s="7" t="str">
-        <v>Drenaje (pluvial)</v>
+        <v>Telecomunicaciones y datos</v>
       </c>
       <c r="G7" s="7" t="str">
         <v>Activo físico</v>
@@ -7570,19 +7586,19 @@
         <v>Inundación</v>
       </c>
       <c r="B8" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="7" t="str">
         <v>ELO</v>
       </c>
       <c r="D8" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E8" s="7" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F8" s="7" t="str">
-        <v>Telecomunicaciones y datos</v>
+        <v>Accesos ferroviarios y terminales ferroportuarias</v>
       </c>
       <c r="G8" s="7" t="str">
         <v>Activo físico</v>
@@ -7620,19 +7636,19 @@
         <v>Inundación</v>
       </c>
       <c r="B9" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="str">
         <v>ELO</v>
       </c>
       <c r="D9" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E9" s="7" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F9" s="7" t="str">
-        <v>Accesos ferroviarios y terminales ferroportuarias</v>
+        <v>Accesos viarios</v>
       </c>
       <c r="G9" s="7" t="str">
         <v>Activo físico</v>
@@ -7670,19 +7686,19 @@
         <v>Inundación</v>
       </c>
       <c r="B10" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="str">
         <v>ELO</v>
       </c>
       <c r="D10" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E10" s="7" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F10" s="7" t="str">
-        <v>Accesos viarios</v>
+        <v>Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)</v>
       </c>
       <c r="G10" s="7" t="str">
         <v>Activo físico</v>
@@ -7720,22 +7736,22 @@
         <v>Inundación</v>
       </c>
       <c r="B11" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="7" t="str">
         <v>ELO</v>
       </c>
       <c r="D11" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E11" s="7" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F11" s="7" t="str">
-        <v>Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)</v>
+        <v>Manipulación de mercancía</v>
       </c>
       <c r="G11" s="7" t="str">
-        <v>Activo físico</v>
+        <v>Operacional (servicios)</v>
       </c>
       <c r="H11" s="7" t="str">
         <v/>
@@ -7770,22 +7786,22 @@
         <v>Inundación</v>
       </c>
       <c r="B12" s="7">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7" t="str">
         <v>ELO</v>
       </c>
       <c r="D12" s="7" t="str">
-        <v>Inundación</v>
+        <v>Inundación costera</v>
       </c>
       <c r="E12" s="7" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F12" s="7" t="str">
-        <v>Manipulación de mercancía</v>
+        <v>Zonas de Actividad Logística</v>
       </c>
       <c r="G12" s="7" t="str">
-        <v>Operacional (servicios)</v>
+        <v>Activo físico</v>
       </c>
       <c r="H12" s="7" t="str">
         <v/>
@@ -7820,7 +7836,7 @@
         <v>Inundación</v>
       </c>
       <c r="B13" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7" t="str">
         <v>ELO</v>
@@ -7832,7 +7848,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F13" s="7" t="str">
-        <v>Zonas de Actividad Logística</v>
+        <v>Astilleros, diques secos, varaderos</v>
       </c>
       <c r="G13" s="7" t="str">
         <v>Activo físico</v>
@@ -7870,7 +7886,7 @@
         <v>Inundación</v>
       </c>
       <c r="B14" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="7" t="str">
         <v>ELO</v>
@@ -7882,7 +7898,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F14" s="7" t="str">
-        <v>Astilleros, diques secos, varaderos</v>
+        <v>Tanques de almacenamiento</v>
       </c>
       <c r="G14" s="7" t="str">
         <v>Activo físico</v>
@@ -7920,7 +7936,7 @@
         <v>Inundación</v>
       </c>
       <c r="B15" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" s="7" t="str">
         <v>ELO</v>
@@ -7932,7 +7948,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F15" s="7" t="str">
-        <v>Tanques de almacenamiento</v>
+        <v>Depósito /Almacenamiento</v>
       </c>
       <c r="G15" s="7" t="str">
         <v>Activo físico</v>
@@ -7970,7 +7986,7 @@
         <v>Inundación</v>
       </c>
       <c r="B16" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" s="7" t="str">
         <v>ELO</v>
@@ -7982,7 +7998,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F16" s="7" t="str">
-        <v>Depósito /Almacenamiento</v>
+        <v>Grúas de muelle</v>
       </c>
       <c r="G16" s="7" t="str">
         <v>Activo físico</v>
@@ -8020,7 +8036,7 @@
         <v>Inundación</v>
       </c>
       <c r="B17" s="7">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" s="7" t="str">
         <v>ELO</v>
@@ -8032,7 +8048,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F17" s="7" t="str">
-        <v>Grúas de muelle</v>
+        <v>Maquinaria de patio</v>
       </c>
       <c r="G17" s="7" t="str">
         <v>Activo físico</v>
@@ -8070,7 +8086,7 @@
         <v>Inundación</v>
       </c>
       <c r="B18" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" s="7" t="str">
         <v>ELO</v>
@@ -8082,7 +8098,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F18" s="7" t="str">
-        <v>Maquinaria de patio</v>
+        <v>Transporte de semiremolques</v>
       </c>
       <c r="G18" s="7" t="str">
         <v>Activo físico</v>
@@ -8120,7 +8136,7 @@
         <v>Inundación</v>
       </c>
       <c r="B19" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="7" t="str">
         <v>ELO</v>
@@ -8132,7 +8148,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F19" s="7" t="str">
-        <v>Transporte de semiremolques</v>
+        <v>Almacenamiento</v>
       </c>
       <c r="G19" s="7" t="str">
         <v>Activo físico</v>
@@ -8170,7 +8186,7 @@
         <v>Inundación</v>
       </c>
       <c r="B20" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="7" t="str">
         <v>ELO</v>
@@ -8182,7 +8198,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F20" s="7" t="str">
-        <v>Almacenamiento</v>
+        <v>Grúa de muelle</v>
       </c>
       <c r="G20" s="7" t="str">
         <v>Activo físico</v>
@@ -8220,7 +8236,7 @@
         <v>Inundación</v>
       </c>
       <c r="B21" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C21" s="7" t="str">
         <v>ELO</v>
@@ -8232,7 +8248,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F21" s="7" t="str">
-        <v>Grúa de muelle</v>
+        <v>Campa y aparcamiento</v>
       </c>
       <c r="G21" s="7" t="str">
         <v>Activo físico</v>
@@ -8270,7 +8286,7 @@
         <v>Inundación</v>
       </c>
       <c r="B22" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C22" s="7" t="str">
         <v>ELO</v>
@@ -8282,7 +8298,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F22" s="7" t="str">
-        <v>Campa y aparcamiento</v>
+        <v>Estación marítima</v>
       </c>
       <c r="G22" s="7" t="str">
         <v>Activo físico</v>
@@ -8320,7 +8336,7 @@
         <v>Inundación</v>
       </c>
       <c r="B23" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" s="7" t="str">
         <v>ELO</v>
@@ -8332,10 +8348,10 @@
         <v>Inundación costera</v>
       </c>
       <c r="F23" s="7" t="str">
-        <v>Estación marítima</v>
+        <v>Suministros al pesquero (agua, combustible y hielo)</v>
       </c>
       <c r="G23" s="7" t="str">
-        <v>Activo físico</v>
+        <v>Operacional (servicios)</v>
       </c>
       <c r="H23" s="7" t="str">
         <v/>
@@ -8370,7 +8386,7 @@
         <v>Inundación</v>
       </c>
       <c r="B24" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C24" s="7" t="str">
         <v>ELO</v>
@@ -8382,10 +8398,10 @@
         <v>Inundación costera</v>
       </c>
       <c r="F24" s="7" t="str">
-        <v>Suministros al pesquero (agua, combustible y hielo)</v>
+        <v>Lonja</v>
       </c>
       <c r="G24" s="7" t="str">
-        <v>Operacional (servicios)</v>
+        <v>Activo físico</v>
       </c>
       <c r="H24" s="7" t="str">
         <v/>
@@ -8420,7 +8436,7 @@
         <v>Inundación</v>
       </c>
       <c r="B25" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C25" s="7" t="str">
         <v>ELO</v>
@@ -8432,10 +8448,10 @@
         <v>Inundación costera</v>
       </c>
       <c r="F25" s="7" t="str">
-        <v>Lonja</v>
+        <v>Servicio de marinas y puertos deportivos</v>
       </c>
       <c r="G25" s="7" t="str">
-        <v>Activo físico</v>
+        <v>Operacional (servicios)</v>
       </c>
       <c r="H25" s="7" t="str">
         <v/>
@@ -8470,7 +8486,7 @@
         <v>Inundación</v>
       </c>
       <c r="B26" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" s="7" t="str">
         <v>ELO</v>
@@ -8482,10 +8498,10 @@
         <v>Inundación costera</v>
       </c>
       <c r="F26" s="7" t="str">
-        <v>Servicio de marinas y puertos deportivos</v>
+        <v>Equipamientos culturales o deportivos</v>
       </c>
       <c r="G26" s="7" t="str">
-        <v>Operacional (servicios)</v>
+        <v>Activo físico</v>
       </c>
       <c r="H26" s="7" t="str">
         <v/>
@@ -8520,10 +8536,10 @@
         <v>Inundación</v>
       </c>
       <c r="B27" s="7">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="7" t="str">
-        <v>ELO</v>
+        <v>ELS</v>
       </c>
       <c r="D27" s="7" t="str">
         <v>Inundación</v>
@@ -8532,7 +8548,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F27" s="7" t="str">
-        <v>Equipamientos culturales o deportivos</v>
+        <v>Superficies</v>
       </c>
       <c r="G27" s="7" t="str">
         <v>Activo físico</v>
@@ -8570,7 +8586,7 @@
         <v>Inundación</v>
       </c>
       <c r="B28" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" s="5" t="str">
         <v>ELS</v>
@@ -8582,7 +8598,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F28" s="5" t="str">
-        <v>Superficies</v>
+        <v>Pavimentos</v>
       </c>
       <c r="G28" s="5" t="str">
         <v>Activo físico</v>
@@ -8620,7 +8636,7 @@
         <v>Inundación</v>
       </c>
       <c r="B29" s="5">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C29" s="5" t="str">
         <v>ELS</v>
@@ -8632,7 +8648,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F29" s="5" t="str">
-        <v>Pavimentos</v>
+        <v>Electricidad</v>
       </c>
       <c r="G29" s="5" t="str">
         <v>Activo físico</v>
@@ -8670,7 +8686,7 @@
         <v>Inundación</v>
       </c>
       <c r="B30" s="5">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" s="5" t="str">
         <v>ELS</v>
@@ -8682,7 +8698,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F30" s="5" t="str">
-        <v>Electricidad</v>
+        <v>Alumbrado</v>
       </c>
       <c r="G30" s="5" t="str">
         <v>Activo físico</v>
@@ -8720,7 +8736,7 @@
         <v>Inundación</v>
       </c>
       <c r="B31" s="5">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C31" s="5" t="str">
         <v>ELS</v>
@@ -8732,7 +8748,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F31" s="5" t="str">
-        <v>Alumbrado</v>
+        <v>Suministro de agua</v>
       </c>
       <c r="G31" s="5" t="str">
         <v>Activo físico</v>
@@ -8770,19 +8786,19 @@
         <v>Inundación</v>
       </c>
       <c r="B32" s="5">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C32" s="5" t="str">
         <v>ELS</v>
       </c>
       <c r="D32" s="5" t="str">
-        <v>Inundación</v>
+        <v>Deterioro debido a inundación</v>
       </c>
       <c r="E32" s="5" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F32" s="5" t="str">
-        <v>Suministro de agua</v>
+        <v>Drenaje (pluvial)</v>
       </c>
       <c r="G32" s="5" t="str">
         <v>Activo físico</v>
@@ -8820,19 +8836,19 @@
         <v>Inundación</v>
       </c>
       <c r="B33" s="5">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="5" t="str">
         <v>ELS</v>
       </c>
       <c r="D33" s="5" t="str">
-        <v>Deterioro debido a inundación</v>
+        <v>Inundación</v>
       </c>
       <c r="E33" s="5" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F33" s="5" t="str">
-        <v>Drenaje (pluvial)</v>
+        <v>Telecomunicaciones y datos</v>
       </c>
       <c r="G33" s="5" t="str">
         <v>Activo físico</v>
@@ -8870,7 +8886,7 @@
         <v>Inundación</v>
       </c>
       <c r="B34" s="5">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C34" s="5" t="str">
         <v>ELS</v>
@@ -8882,7 +8898,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F34" s="5" t="str">
-        <v>Telecomunicaciones y datos</v>
+        <v>Instalación OPS</v>
       </c>
       <c r="G34" s="5" t="str">
         <v>Activo físico</v>
@@ -8920,7 +8936,7 @@
         <v>Inundación</v>
       </c>
       <c r="B35" s="5">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C35" s="5" t="str">
         <v>ELS</v>
@@ -8932,7 +8948,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F35" s="5" t="str">
-        <v>Instalación OPS</v>
+        <v>Accesos ferroviarios y terminales ferroportuarias</v>
       </c>
       <c r="G35" s="5" t="str">
         <v>Activo físico</v>
@@ -8970,7 +8986,7 @@
         <v>Inundación</v>
       </c>
       <c r="B36" s="5">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C36" s="5" t="str">
         <v>ELS</v>
@@ -8982,7 +8998,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F36" s="5" t="str">
-        <v>Accesos ferroviarios y terminales ferroportuarias</v>
+        <v>Accesos viarios</v>
       </c>
       <c r="G36" s="5" t="str">
         <v>Activo físico</v>
@@ -9020,7 +9036,7 @@
         <v>Inundación</v>
       </c>
       <c r="B37" s="5">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C37" s="5" t="str">
         <v>ELS</v>
@@ -9032,7 +9048,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F37" s="5" t="str">
-        <v>Accesos viarios</v>
+        <v>Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)</v>
       </c>
       <c r="G37" s="5" t="str">
         <v>Activo físico</v>
@@ -9070,7 +9086,7 @@
         <v>Inundación</v>
       </c>
       <c r="B38" s="5">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C38" s="5" t="str">
         <v>ELS</v>
@@ -9082,7 +9098,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F38" s="5" t="str">
-        <v>Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)</v>
+        <v>Zonas de Actividad Logística</v>
       </c>
       <c r="G38" s="5" t="str">
         <v>Activo físico</v>
@@ -9120,7 +9136,7 @@
         <v>Inundación</v>
       </c>
       <c r="B39" s="5">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C39" s="5" t="str">
         <v>ELS</v>
@@ -9132,7 +9148,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F39" s="5" t="str">
-        <v>Zonas de Actividad Logística</v>
+        <v>Astilleros, diques secos, varaderos</v>
       </c>
       <c r="G39" s="5" t="str">
         <v>Activo físico</v>
@@ -9170,19 +9186,19 @@
         <v>Inundación</v>
       </c>
       <c r="B40" s="5">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" s="5" t="str">
         <v>ELS</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Inundación</v>
+        <v>Daño estructural debido a inundación</v>
       </c>
       <c r="E40" s="5" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F40" s="5" t="str">
-        <v>Astilleros, diques secos, varaderos</v>
+        <v>Sistemas de carga y descarga (Tuberías)</v>
       </c>
       <c r="G40" s="5" t="str">
         <v>Activo físico</v>
@@ -9220,19 +9236,19 @@
         <v>Inundación</v>
       </c>
       <c r="B41" s="5">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C41" s="5" t="str">
         <v>ELS</v>
       </c>
       <c r="D41" s="5" t="str">
-        <v>Daño estructural debido a inundación</v>
+        <v>Inundación</v>
       </c>
       <c r="E41" s="5" t="str">
         <v>Inundación costera</v>
       </c>
       <c r="F41" s="5" t="str">
-        <v>Sistemas de carga y descarga (Tuberías)</v>
+        <v>Medios de carga/descarga</v>
       </c>
       <c r="G41" s="5" t="str">
         <v>Activo físico</v>
@@ -9270,7 +9286,7 @@
         <v>Inundación</v>
       </c>
       <c r="B42" s="5">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C42" s="5" t="str">
         <v>ELS</v>
@@ -9282,7 +9298,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F42" s="5" t="str">
-        <v>Medios de carga/descarga</v>
+        <v>Tolvas y cintas transportadoras</v>
       </c>
       <c r="G42" s="5" t="str">
         <v>Activo físico</v>
@@ -9320,7 +9336,7 @@
         <v>Inundación</v>
       </c>
       <c r="B43" s="5">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C43" s="5" t="str">
         <v>ELS</v>
@@ -9332,7 +9348,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F43" s="5" t="str">
-        <v>Tolvas y cintas transportadoras</v>
+        <v>Depósito /Almacenamiento</v>
       </c>
       <c r="G43" s="5" t="str">
         <v>Activo físico</v>
@@ -9370,7 +9386,7 @@
         <v>Inundación</v>
       </c>
       <c r="B44" s="5">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C44" s="5" t="str">
         <v>ELS</v>
@@ -9382,7 +9398,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F44" s="5" t="str">
-        <v>Depósito /Almacenamiento</v>
+        <v>Maquinaria de patio</v>
       </c>
       <c r="G44" s="5" t="str">
         <v>Activo físico</v>
@@ -9420,7 +9436,7 @@
         <v>Inundación</v>
       </c>
       <c r="B45" s="5">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C45" s="5" t="str">
         <v>ELS</v>
@@ -9432,7 +9448,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F45" s="5" t="str">
-        <v>Maquinaria de patio</v>
+        <v>Transporte de semiremolques</v>
       </c>
       <c r="G45" s="5" t="str">
         <v>Activo físico</v>
@@ -9470,7 +9486,7 @@
         <v>Inundación</v>
       </c>
       <c r="B46" s="5">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C46" s="5" t="str">
         <v>ELS</v>
@@ -9482,7 +9498,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F46" s="5" t="str">
-        <v>Transporte de semiremolques</v>
+        <v>Almacenamiento</v>
       </c>
       <c r="G46" s="5" t="str">
         <v>Activo físico</v>
@@ -9520,7 +9536,7 @@
         <v>Inundación</v>
       </c>
       <c r="B47" s="5">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C47" s="5" t="str">
         <v>ELS</v>
@@ -9532,7 +9548,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F47" s="5" t="str">
-        <v>Almacenamiento</v>
+        <v>Campa y aparcamiento</v>
       </c>
       <c r="G47" s="5" t="str">
         <v>Activo físico</v>
@@ -9570,7 +9586,7 @@
         <v>Inundación</v>
       </c>
       <c r="B48" s="5">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C48" s="5" t="str">
         <v>ELS</v>
@@ -9582,7 +9598,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F48" s="5" t="str">
-        <v>Campa y aparcamiento</v>
+        <v>Estación marítima</v>
       </c>
       <c r="G48" s="5" t="str">
         <v>Activo físico</v>
@@ -9620,7 +9636,7 @@
         <v>Inundación</v>
       </c>
       <c r="B49" s="5">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C49" s="5" t="str">
         <v>ELS</v>
@@ -9632,7 +9648,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F49" s="5" t="str">
-        <v>Estación marítima</v>
+        <v>Lonja</v>
       </c>
       <c r="G49" s="5" t="str">
         <v>Activo físico</v>
@@ -9670,7 +9686,7 @@
         <v>Inundación</v>
       </c>
       <c r="B50" s="5">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C50" s="5" t="str">
         <v>ELS</v>
@@ -9682,10 +9698,10 @@
         <v>Inundación costera</v>
       </c>
       <c r="F50" s="5" t="str">
-        <v>Lonja</v>
+        <v>Servicio de marinas y puertos deportivos</v>
       </c>
       <c r="G50" s="5" t="str">
-        <v>Activo físico</v>
+        <v>Operacional (servicios)</v>
       </c>
       <c r="H50" s="5" t="str">
         <v/>
@@ -9720,7 +9736,7 @@
         <v>Inundación</v>
       </c>
       <c r="B51" s="5">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C51" s="5" t="str">
         <v>ELS</v>
@@ -9732,10 +9748,10 @@
         <v>Inundación costera</v>
       </c>
       <c r="F51" s="5" t="str">
-        <v>Servicio de marinas y puertos deportivos</v>
+        <v>Accesos peatonales, Paseo marítimo y carril bici</v>
       </c>
       <c r="G51" s="5" t="str">
-        <v>Operacional (servicios)</v>
+        <v>Activo físico</v>
       </c>
       <c r="H51" s="5" t="str">
         <v/>
@@ -9770,7 +9786,7 @@
         <v>Inundación</v>
       </c>
       <c r="B52" s="5">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C52" s="5" t="str">
         <v>ELS</v>
@@ -9782,7 +9798,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F52" s="5" t="str">
-        <v>Accesos peatonales, Paseo marítimo y carril bici</v>
+        <v>Zona de ocio</v>
       </c>
       <c r="G52" s="5" t="str">
         <v>Activo físico</v>
@@ -9820,7 +9836,7 @@
         <v>Inundación</v>
       </c>
       <c r="B53" s="5">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C53" s="5" t="str">
         <v>ELS</v>
@@ -9832,7 +9848,7 @@
         <v>Inundación costera</v>
       </c>
       <c r="F53" s="5" t="str">
-        <v>Zona de ocio</v>
+        <v>Equipamientos culturales o deportivos</v>
       </c>
       <c r="G53" s="5" t="str">
         <v>Activo físico</v>
@@ -9866,54 +9882,22 @@
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="str">
-        <v>Inundación</v>
-      </c>
-      <c r="B54" s="5">
-        <v>149</v>
-      </c>
-      <c r="C54" s="5" t="str">
-        <v>ELS</v>
-      </c>
-      <c r="D54" s="5" t="str">
-        <v>Inundación</v>
-      </c>
-      <c r="E54" s="5" t="str">
-        <v>Inundación costera</v>
-      </c>
-      <c r="F54" s="5" t="str">
-        <v>Equipamientos culturales o deportivos</v>
-      </c>
-      <c r="G54" s="5" t="str">
-        <v>Activo físico</v>
-      </c>
-      <c r="H54" s="5" t="str">
-        <v/>
-      </c>
-      <c r="I54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="J54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="K54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="L54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="M54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="N54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="O54" s="16" t="str">
-        <v/>
-      </c>
-      <c r="P54" s="16" t="str">
-        <v/>
-      </c>
+      <c r="A54" s="16"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14075,7 +14059,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ca="1" si="0"/>
@@ -14107,7 +14091,7 @@
       </c>
       <c r="M2" s="3">
         <f ca="1">+SUM(A2:L2)</f>
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="N2" s="3">
         <f>+COUNT('ListRelacion impactos-indicador'!A2:A182)</f>
@@ -14115,7 +14099,7 @@
       </c>
       <c r="O2" s="3">
         <f ca="1">+N2-M2</f>
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -14135,9 +14119,9 @@
         <f t="array" aca="1" ref="D3:D14" ca="1">_xlfn._xlws.FILTER(INDIRECT("'"&amp;D1&amp;"'!A2:A176"),INDIRECT("'"&amp;D1&amp;"'!A2:A176")&lt;&gt;"","")</f>
         <v>Temperatura</v>
       </c>
-      <c r="E3" s="18" t="str" cm="1">
-        <f t="array" aca="1" ref="E3:E55" ca="1">_xlfn._xlws.FILTER(INDIRECT("'"&amp;E1&amp;"'!A2:A176"),INDIRECT("'"&amp;E1&amp;"'!A2:A176")&lt;&gt;"","")</f>
-        <v>Inundación</v>
+      <c r="E3" s="18" t="e" cm="1">
+        <f t="array" aca="1" ref="E3" ca="1">_xlfn._xlws.FILTER(INDIRECT("'"&amp;E1&amp;"'!A2:A176"),INDIRECT("'"&amp;E1&amp;"'!A2:A176")&lt;&gt;"","")</f>
+        <v>#REF!</v>
       </c>
       <c r="F3" s="18" t="str" cm="1">
         <f t="array" aca="1" ref="F3:F4" ca="1">_xlfn._xlws.FILTER(INDIRECT("'"&amp;F1&amp;"'!A2:A176"),INDIRECT("'"&amp;F1&amp;"'!A2:A176")&lt;&gt;"","")</f>
@@ -14197,10 +14181,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E4" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E4" s="18"/>
       <c r="F4" s="18" t="str">
         <f ca="1"/>
         <v>Precipitación</v>
@@ -14258,10 +14239,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E5" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E5" s="18"/>
       <c r="G5" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14311,10 +14289,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E6" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E6" s="18"/>
       <c r="G6" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14360,10 +14335,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E7" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E7" s="18"/>
       <c r="G7" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14401,10 +14373,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E8" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E8" s="18"/>
       <c r="G8" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14442,10 +14411,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E9" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E9" s="18"/>
       <c r="G9" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14483,10 +14449,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E10" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E10" s="18"/>
       <c r="G10" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14524,10 +14487,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E11" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E11" s="18"/>
       <c r="G11" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14565,10 +14525,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E12" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E12" s="18"/>
       <c r="G12" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14606,10 +14563,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E13" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E13" s="18"/>
       <c r="G13" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14643,10 +14597,7 @@
         <f ca="1"/>
         <v>Temperatura</v>
       </c>
-      <c r="E14" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E14" s="18"/>
       <c r="G14" s="18" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14676,10 +14627,7 @@
         <f ca="1"/>
         <v>Compuestos</v>
       </c>
-      <c r="E15" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E15" s="18"/>
       <c r="G15" t="str">
         <f ca="1"/>
         <v>Agitación-Oleaje</v>
@@ -14709,10 +14657,7 @@
         <f ca="1"/>
         <v>Compuestos</v>
       </c>
-      <c r="E16" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E16" s="18"/>
       <c r="H16" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14738,10 +14683,7 @@
         <f ca="1"/>
         <v>Compuestos</v>
       </c>
-      <c r="E17" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E17" s="18"/>
       <c r="H17" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14767,10 +14709,7 @@
         <f ca="1"/>
         <v>Compuestos</v>
       </c>
-      <c r="E18" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E18" s="18"/>
       <c r="H18" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14792,10 +14731,7 @@
         <f ca="1"/>
         <v>Compuestos</v>
       </c>
-      <c r="E19" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E19" s="18"/>
       <c r="H19" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14817,10 +14753,7 @@
         <f ca="1"/>
         <v>Compuestos</v>
       </c>
-      <c r="E20" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E20" s="18"/>
       <c r="H20" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14838,10 +14771,7 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E21" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E21" s="18"/>
       <c r="H21" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14859,10 +14789,7 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E22" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E22" s="18"/>
       <c r="H22" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14880,10 +14807,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E23" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E23" s="18"/>
       <c r="H23" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14901,10 +14825,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E24" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E24" s="18"/>
       <c r="H24" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14922,10 +14843,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E25" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E25" s="18"/>
       <c r="H25" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14943,10 +14861,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E26" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E26" s="18"/>
       <c r="H26" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14964,10 +14879,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E27" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E27" s="18"/>
       <c r="H27" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -14985,10 +14897,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E28" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E28" s="18"/>
       <c r="H28" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15006,10 +14915,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E29" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E29" s="18"/>
       <c r="H29" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15027,10 +14933,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E30" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E30" s="18"/>
       <c r="H30" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15048,10 +14951,7 @@
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E31" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E31" s="18"/>
       <c r="H31" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15069,10 +14969,7 @@
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E32" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E32" s="18"/>
       <c r="H32" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15090,10 +14987,7 @@
       </c>
     </row>
     <row r="33" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E33" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E33" s="18"/>
       <c r="H33" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15111,10 +15005,7 @@
       </c>
     </row>
     <row r="34" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E34" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E34" s="18"/>
       <c r="H34" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15132,10 +15023,7 @@
       </c>
     </row>
     <row r="35" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E35" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E35" s="18"/>
       <c r="H35" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15153,10 +15041,7 @@
       </c>
     </row>
     <row r="36" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E36" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E36" s="18"/>
       <c r="H36" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15174,10 +15059,7 @@
       </c>
     </row>
     <row r="37" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E37" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E37" s="18"/>
       <c r="H37" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15195,10 +15077,7 @@
       </c>
     </row>
     <row r="38" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E38" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E38" s="18"/>
       <c r="H38" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15216,10 +15095,7 @@
       </c>
     </row>
     <row r="39" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E39" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E39" s="18"/>
       <c r="H39" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15237,10 +15113,7 @@
       </c>
     </row>
     <row r="40" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E40" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E40" s="18"/>
       <c r="H40" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15258,10 +15131,7 @@
       </c>
     </row>
     <row r="41" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E41" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E41" s="18"/>
       <c r="H41" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15279,10 +15149,7 @@
       </c>
     </row>
     <row r="42" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E42" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E42" s="18"/>
       <c r="H42" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15300,10 +15167,7 @@
       </c>
     </row>
     <row r="43" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E43" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E43" s="18"/>
       <c r="H43" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15321,10 +15185,7 @@
       </c>
     </row>
     <row r="44" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E44" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E44" s="18"/>
       <c r="H44" s="18" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15342,10 +15203,7 @@
       </c>
     </row>
     <row r="45" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E45" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E45" s="18"/>
       <c r="H45" t="str">
         <f ca="1"/>
         <v>Viento</v>
@@ -15363,10 +15221,7 @@
       </c>
     </row>
     <row r="46" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E46" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E46" s="18"/>
       <c r="M46">
         <v>44</v>
       </c>
@@ -15380,10 +15235,7 @@
       </c>
     </row>
     <row r="47" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E47" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E47" s="18"/>
       <c r="M47">
         <v>45</v>
       </c>
@@ -15397,10 +15249,7 @@
       </c>
     </row>
     <row r="48" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E48" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E48" s="18"/>
       <c r="M48">
         <v>46</v>
       </c>
@@ -15414,10 +15263,7 @@
       </c>
     </row>
     <row r="49" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E49" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E49" s="18"/>
       <c r="M49">
         <v>47</v>
       </c>
@@ -15431,10 +15277,7 @@
       </c>
     </row>
     <row r="50" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E50" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E50" s="18"/>
       <c r="M50">
         <v>48</v>
       </c>
@@ -15448,10 +15291,7 @@
       </c>
     </row>
     <row r="51" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E51" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E51" s="18"/>
       <c r="M51">
         <v>49</v>
       </c>
@@ -15465,10 +15305,7 @@
       </c>
     </row>
     <row r="52" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E52" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E52" s="18"/>
       <c r="M52">
         <v>50</v>
       </c>
@@ -15482,10 +15319,7 @@
       </c>
     </row>
     <row r="53" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E53" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E53" s="18"/>
       <c r="M53">
         <v>51</v>
       </c>
@@ -15499,10 +15333,7 @@
       </c>
     </row>
     <row r="54" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E54" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E54" s="18"/>
       <c r="M54">
         <v>52</v>
       </c>
@@ -15516,10 +15347,7 @@
       </c>
     </row>
     <row r="55" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E55" s="18" t="str">
-        <f ca="1"/>
-        <v>Inundación</v>
-      </c>
+      <c r="E55" s="18"/>
       <c r="M55">
         <v>53</v>
       </c>

--- a/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
+++ b/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BA24E1-C52A-42F2-B5DD-0313D4EF765E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330D6582-3FEA-4DF7-9F25-1361EA04368D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListRelacion impactos-indicador" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">Compuestos!$A$1:$P$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">Corriente!$A$1:$P$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Inundación costera'!$A$1:$P$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ListRelacion impactos-indicador'!$A$1:$P$182</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ListRelacion impactos-indicador'!$A$1:$P$179</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">Precipitación!$A$1:$P$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">Rebase!$A$1:$P$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">Temperatura!$A$1:$P$13</definedName>
@@ -2833,7 +2833,7 @@
       <c r="O51" s="17"/>
       <c r="P51" s="17"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
         <v>51</v>
       </c>
@@ -2866,7 +2866,7 @@
       <c r="O52" s="17"/>
       <c r="P52" s="17"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="17">
         <v>52</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="O54" s="17"/>
       <c r="P54" s="17"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17">
         <v>54</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="O58" s="17"/>
       <c r="P58" s="17"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17">
         <v>58</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="O59" s="17"/>
       <c r="P59" s="17"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17">
         <v>59</v>
       </c>
@@ -3130,7 +3130,7 @@
       <c r="O60" s="17"/>
       <c r="P60" s="17"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17">
         <v>60</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="O62" s="17"/>
       <c r="P62" s="17"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17">
         <v>62</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="O65" s="17"/>
       <c r="P65" s="17"/>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="17">
         <v>65</v>
       </c>
@@ -3328,7 +3328,7 @@
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <v>66</v>
       </c>
@@ -3361,7 +3361,7 @@
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="17">
         <v>67</v>
       </c>
@@ -3384,7 +3384,9 @@
         <f>IF(C68="","",IFERROR(IF(INDEX(UnidadMedida!$B$1:$B$30,MATCH(C68,UnidadMedida!$A$1:$A$30,0))="","",INDEX(UnidadMedida!$B$1:$B$30,MATCH(C68,UnidadMedida!$A$1:$A$30,0))),""))</f>
         <v>m/s</v>
       </c>
-      <c r="H68" s="17"/>
+      <c r="H68" s="17">
+        <v>8</v>
+      </c>
       <c r="I68" s="17"/>
       <c r="J68" s="17"/>
       <c r="K68" s="17"/>
@@ -3394,7 +3396,7 @@
       <c r="O68" s="17"/>
       <c r="P68" s="17"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
         <v>68</v>
       </c>
@@ -7178,14 +7180,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P182" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}">
-    <filterColumn colId="1">
+    <filterColumn colId="4">
       <filters>
-        <filter val="ELO"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Inundación costera"/>
+        <filter val="Personal del puerto"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -11699,8 +11696,8 @@
       <c r="G12" s="5" t="str">
         <v>Operacional (servicios)</v>
       </c>
-      <c r="H12" s="5" t="str">
-        <v/>
+      <c r="H12" s="5">
+        <v>8</v>
       </c>
       <c r="I12" s="5" t="str">
         <v/>

--- a/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
+++ b/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330D6582-3FEA-4DF7-9F25-1361EA04368D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9769A492-2769-4A2F-9DAA-B182B7DDF90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListRelacion impactos-indicador" sheetId="3" r:id="rId1"/>
@@ -3196,7 +3196,7 @@
       <c r="O62" s="17"/>
       <c r="P62" s="17"/>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="17">
         <v>62</v>
       </c>
@@ -3229,7 +3229,7 @@
       <c r="O63" s="17"/>
       <c r="P63" s="17"/>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <v>63</v>
       </c>
@@ -3262,7 +3262,7 @@
       <c r="O64" s="17"/>
       <c r="P64" s="17"/>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <v>64</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="O65" s="17"/>
       <c r="P65" s="17"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17">
         <v>65</v>
       </c>
@@ -3328,7 +3328,7 @@
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <v>66</v>
       </c>
@@ -3361,7 +3361,7 @@
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17">
         <v>67</v>
       </c>
@@ -7182,7 +7182,7 @@
   <autoFilter ref="A1:P182" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}">
     <filterColumn colId="4">
       <filters>
-        <filter val="Personal del puerto"/>
+        <filter val="Manipulación de mercancía"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
+++ b/data_modelos/2_Relación_umbrales_y_curvas_de_daño_vs_activos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9769A492-2769-4A2F-9DAA-B182B7DDF90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF77E22-C286-4064-A5D1-72F1E0D1260F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListRelacion impactos-indicador" sheetId="3" r:id="rId1"/>
@@ -957,7 +957,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1029,7 +1028,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -1068,7 +1067,7 @@
       </c>
       <c r="P2" s="17"/>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -1103,7 +1102,7 @@
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -1138,7 +1137,7 @@
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>4</v>
       </c>
@@ -1177,7 +1176,7 @@
       </c>
       <c r="P5" s="17"/>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -1216,7 +1215,7 @@
       </c>
       <c r="P6" s="17"/>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>6</v>
       </c>
@@ -1251,7 +1250,7 @@
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>7</v>
       </c>
@@ -1286,7 +1285,7 @@
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>8</v>
       </c>
@@ -1321,7 +1320,7 @@
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>9</v>
       </c>
@@ -1356,7 +1355,7 @@
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>10</v>
       </c>
@@ -1391,7 +1390,7 @@
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>11</v>
       </c>
@@ -1426,7 +1425,7 @@
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>12</v>
       </c>
@@ -1461,7 +1460,7 @@
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>13</v>
       </c>
@@ -1496,7 +1495,7 @@
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>14</v>
       </c>
@@ -1531,7 +1530,7 @@
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>15</v>
       </c>
@@ -1566,7 +1565,7 @@
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>16</v>
       </c>
@@ -1601,7 +1600,7 @@
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>17</v>
       </c>
@@ -1636,7 +1635,7 @@
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>18</v>
       </c>
@@ -1671,7 +1670,7 @@
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>19</v>
       </c>
@@ -1706,7 +1705,7 @@
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>20</v>
       </c>
@@ -1741,7 +1740,7 @@
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>21</v>
       </c>
@@ -1776,7 +1775,7 @@
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>22</v>
       </c>
@@ -1811,7 +1810,7 @@
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>23</v>
       </c>
@@ -1846,7 +1845,7 @@
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>24</v>
       </c>
@@ -1881,7 +1880,7 @@
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>25</v>
       </c>
@@ -1916,7 +1915,7 @@
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>26</v>
       </c>
@@ -1951,7 +1950,7 @@
       <c r="O27" s="17"/>
       <c r="P27" s="17"/>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>27</v>
       </c>
@@ -1986,7 +1985,7 @@
       <c r="O28" s="17"/>
       <c r="P28" s="17"/>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <v>28</v>
       </c>
@@ -2019,7 +2018,7 @@
       <c r="O29" s="17"/>
       <c r="P29" s="17"/>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <v>29</v>
       </c>
@@ -2052,7 +2051,7 @@
       <c r="O30" s="17"/>
       <c r="P30" s="17"/>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <v>30</v>
       </c>
@@ -2085,7 +2084,7 @@
       <c r="O31" s="17"/>
       <c r="P31" s="17"/>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <v>31</v>
       </c>
@@ -2118,7 +2117,7 @@
       <c r="O32" s="17"/>
       <c r="P32" s="17"/>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <v>32</v>
       </c>
@@ -2151,7 +2150,7 @@
       <c r="O33" s="17"/>
       <c r="P33" s="17"/>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <v>33</v>
       </c>
@@ -2184,7 +2183,7 @@
       <c r="O34" s="17"/>
       <c r="P34" s="17"/>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <v>34</v>
       </c>
@@ -2217,7 +2216,7 @@
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <v>35</v>
       </c>
@@ -2250,7 +2249,7 @@
       <c r="O36" s="17"/>
       <c r="P36" s="17"/>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <v>36</v>
       </c>
@@ -2285,7 +2284,7 @@
       <c r="O37" s="17"/>
       <c r="P37" s="17"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <v>37</v>
       </c>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="P38" s="17"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <v>38</v>
       </c>
@@ -2367,7 +2366,7 @@
       <c r="O39" s="17"/>
       <c r="P39" s="17"/>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <v>39</v>
       </c>
@@ -2402,7 +2401,7 @@
       <c r="O40" s="17"/>
       <c r="P40" s="17"/>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <v>40</v>
       </c>
@@ -2449,7 +2448,7 @@
       </c>
       <c r="P41" s="17"/>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <v>41</v>
       </c>
@@ -2484,7 +2483,7 @@
       <c r="O42" s="17"/>
       <c r="P42" s="17"/>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <v>42</v>
       </c>
@@ -2519,7 +2518,7 @@
       <c r="O43" s="17"/>
       <c r="P43" s="17"/>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <v>43</v>
       </c>
@@ -2566,7 +2565,7 @@
       </c>
       <c r="P44" s="17"/>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <v>44</v>
       </c>
@@ -2601,7 +2600,7 @@
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <v>45</v>
       </c>
@@ -2648,7 +2647,7 @@
       </c>
       <c r="P46" s="17"/>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <v>46</v>
       </c>
@@ -2683,7 +2682,7 @@
       <c r="O47" s="17"/>
       <c r="P47" s="17"/>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <v>47</v>
       </c>
@@ -2718,7 +2717,7 @@
       <c r="O48" s="17"/>
       <c r="P48" s="17"/>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="17">
         <v>48</v>
       </c>
@@ -2765,7 +2764,7 @@
       </c>
       <c r="P49" s="17"/>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="17">
         <v>49</v>
       </c>
@@ -2800,7 +2799,7 @@
       <c r="O50" s="17"/>
       <c r="P50" s="17"/>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <v>50</v>
       </c>
@@ -2833,7 +2832,7 @@
       <c r="O51" s="17"/>
       <c r="P51" s="17"/>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
         <v>51</v>
       </c>
@@ -2866,7 +2865,7 @@
       <c r="O52" s="17"/>
       <c r="P52" s="17"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="17">
         <v>52</v>
       </c>
@@ -2899,7 +2898,7 @@
       <c r="O53" s="17"/>
       <c r="P53" s="17"/>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="17">
         <v>53</v>
       </c>
@@ -2932,7 +2931,7 @@
       <c r="O54" s="17"/>
       <c r="P54" s="17"/>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="17">
         <v>54</v>
       </c>
@@ -2965,7 +2964,7 @@
       <c r="O55" s="17"/>
       <c r="P55" s="17"/>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="17">
         <v>55</v>
       </c>
@@ -2998,7 +2997,7 @@
       <c r="O56" s="17"/>
       <c r="P56" s="17"/>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
         <v>56</v>
       </c>
@@ -3031,7 +3030,7 @@
       <c r="O57" s="17"/>
       <c r="P57" s="17"/>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="17">
         <v>57</v>
       </c>
@@ -3064,7 +3063,7 @@
       <c r="O58" s="17"/>
       <c r="P58" s="17"/>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="17">
         <v>58</v>
       </c>
@@ -3097,7 +3096,7 @@
       <c r="O59" s="17"/>
       <c r="P59" s="17"/>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="17">
         <v>59</v>
       </c>
@@ -3130,7 +3129,7 @@
       <c r="O60" s="17"/>
       <c r="P60" s="17"/>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="17">
         <v>60</v>
       </c>
@@ -3163,7 +3162,7 @@
       <c r="O61" s="17"/>
       <c r="P61" s="17"/>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="17">
         <v>61</v>
       </c>
@@ -3295,7 +3294,7 @@
       <c r="O65" s="17"/>
       <c r="P65" s="17"/>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="17">
         <v>65</v>
       </c>
@@ -3328,7 +3327,7 @@
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <v>66</v>
       </c>
@@ -3361,7 +3360,7 @@
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="17">
         <v>67</v>
       </c>
@@ -3396,7 +3395,7 @@
       <c r="O68" s="17"/>
       <c r="P68" s="17"/>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
         <v>68</v>
       </c>
@@ -3429,7 +3428,7 @@
       <c r="O69" s="17"/>
       <c r="P69" s="17"/>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="17">
         <v>69</v>
       </c>
@@ -3462,7 +3461,7 @@
       <c r="O70" s="17"/>
       <c r="P70" s="17"/>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="17">
         <v>70</v>
       </c>
@@ -3495,7 +3494,7 @@
       <c r="O71" s="17"/>
       <c r="P71" s="17"/>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="17">
         <v>71</v>
       </c>
@@ -3528,7 +3527,7 @@
       <c r="O72" s="17"/>
       <c r="P72" s="17"/>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="17">
         <v>72</v>
       </c>
@@ -3561,7 +3560,7 @@
       <c r="O73" s="17"/>
       <c r="P73" s="17"/>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="17">
         <v>73</v>
       </c>
@@ -3594,7 +3593,7 @@
       <c r="O74" s="17"/>
       <c r="P74" s="17"/>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="17">
         <v>74</v>
       </c>
@@ -3627,7 +3626,7 @@
       <c r="O75" s="17"/>
       <c r="P75" s="17"/>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="17">
         <v>75</v>
       </c>
@@ -3660,7 +3659,7 @@
       <c r="O76" s="17"/>
       <c r="P76" s="17"/>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="17">
         <v>76</v>
       </c>
@@ -3693,7 +3692,7 @@
       <c r="O77" s="17"/>
       <c r="P77" s="17"/>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="17">
         <v>77</v>
       </c>
@@ -3726,7 +3725,7 @@
       <c r="O78" s="17"/>
       <c r="P78" s="17"/>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="17">
         <v>78</v>
       </c>
@@ -3759,7 +3758,7 @@
       <c r="O79" s="17"/>
       <c r="P79" s="17"/>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="17">
         <v>79</v>
       </c>
@@ -3792,7 +3791,7 @@
       <c r="O80" s="17"/>
       <c r="P80" s="17"/>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="17">
         <v>80</v>
       </c>
@@ -3825,7 +3824,7 @@
       <c r="O81" s="17"/>
       <c r="P81" s="17"/>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="17">
         <v>81</v>
       </c>
@@ -3858,7 +3857,7 @@
       <c r="O82" s="17"/>
       <c r="P82" s="17"/>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="17">
         <v>82</v>
       </c>
@@ -3891,7 +3890,7 @@
       <c r="O83" s="17"/>
       <c r="P83" s="17"/>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="17">
         <v>83</v>
       </c>
@@ -3924,7 +3923,7 @@
       <c r="O84" s="17"/>
       <c r="P84" s="17"/>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="17">
         <v>84</v>
       </c>
@@ -3957,7 +3956,7 @@
       <c r="O85" s="17"/>
       <c r="P85" s="17"/>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="17">
         <v>85</v>
       </c>
@@ -3990,7 +3989,7 @@
       <c r="O86" s="17"/>
       <c r="P86" s="17"/>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="17">
         <v>86</v>
       </c>
@@ -4023,7 +4022,7 @@
       <c r="O87" s="17"/>
       <c r="P87" s="17"/>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="17">
         <v>87</v>
       </c>
@@ -4056,7 +4055,7 @@
       <c r="O88" s="17"/>
       <c r="P88" s="17"/>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="17">
         <v>88</v>
       </c>
@@ -4089,7 +4088,7 @@
       <c r="O89" s="17"/>
       <c r="P89" s="17"/>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="17">
         <v>89</v>
       </c>
@@ -4122,7 +4121,7 @@
       <c r="O90" s="17"/>
       <c r="P90" s="17"/>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="17">
         <v>90</v>
       </c>
@@ -4155,7 +4154,7 @@
       <c r="O91" s="17"/>
       <c r="P91" s="17"/>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="17">
         <v>91</v>
       </c>
@@ -4188,7 +4187,7 @@
       <c r="O92" s="17"/>
       <c r="P92" s="17"/>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="17">
         <v>92</v>
       </c>
@@ -4221,7 +4220,7 @@
       <c r="O93" s="17"/>
       <c r="P93" s="17"/>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="17">
         <v>93</v>
       </c>
@@ -4254,7 +4253,7 @@
       <c r="O94" s="17"/>
       <c r="P94" s="17"/>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="17">
         <v>94</v>
       </c>
@@ -4289,7 +4288,7 @@
       <c r="O95" s="17"/>
       <c r="P95" s="17"/>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="17">
         <v>95</v>
       </c>
@@ -4324,7 +4323,7 @@
       <c r="O96" s="17"/>
       <c r="P96" s="17"/>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="17">
         <v>96</v>
       </c>
@@ -4359,7 +4358,7 @@
       <c r="O97" s="17"/>
       <c r="P97" s="17"/>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="17">
         <v>97</v>
       </c>
@@ -4394,7 +4393,7 @@
       <c r="O98" s="17"/>
       <c r="P98" s="17"/>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="17">
         <v>98</v>
       </c>
@@ -4429,7 +4428,7 @@
       <c r="O99" s="17"/>
       <c r="P99" s="17"/>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="17">
         <v>99</v>
       </c>
@@ -4462,7 +4461,7 @@
       <c r="O100" s="17"/>
       <c r="P100" s="17"/>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="17">
         <v>100</v>
       </c>
@@ -4495,7 +4494,7 @@
       <c r="O101" s="17"/>
       <c r="P101" s="17"/>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="17">
         <v>101</v>
       </c>
@@ -4528,7 +4527,7 @@
       <c r="O102" s="17"/>
       <c r="P102" s="17"/>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="17">
         <v>102</v>
       </c>
@@ -4561,7 +4560,7 @@
       <c r="O103" s="17"/>
       <c r="P103" s="17"/>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="17">
         <v>103</v>
       </c>
@@ -4594,7 +4593,7 @@
       <c r="O104" s="17"/>
       <c r="P104" s="17"/>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="17">
         <v>104</v>
       </c>
@@ -4627,7 +4626,7 @@
       <c r="O105" s="17"/>
       <c r="P105" s="17"/>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="17">
         <v>105</v>
       </c>
@@ -4660,7 +4659,7 @@
       <c r="O106" s="17"/>
       <c r="P106" s="17"/>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="17">
         <v>106</v>
       </c>
@@ -4693,7 +4692,7 @@
       <c r="O107" s="17"/>
       <c r="P107" s="17"/>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="17">
         <v>107</v>
       </c>
@@ -4726,7 +4725,7 @@
       <c r="O108" s="17"/>
       <c r="P108" s="17"/>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="17">
         <v>108</v>
       </c>
@@ -4759,7 +4758,7 @@
       <c r="O109" s="17"/>
       <c r="P109" s="17"/>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="17">
         <v>109</v>
       </c>
@@ -4792,7 +4791,7 @@
       <c r="O110" s="17"/>
       <c r="P110" s="17"/>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="17">
         <v>110</v>
       </c>
@@ -4825,7 +4824,7 @@
       <c r="O111" s="17"/>
       <c r="P111" s="17"/>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="17">
         <v>111</v>
       </c>
@@ -4858,7 +4857,7 @@
       <c r="O112" s="17"/>
       <c r="P112" s="17"/>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="17">
         <v>112</v>
       </c>
@@ -4891,7 +4890,7 @@
       <c r="O113" s="17"/>
       <c r="P113" s="17"/>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="17">
         <v>113</v>
       </c>
@@ -4924,7 +4923,7 @@
       <c r="O114" s="17"/>
       <c r="P114" s="17"/>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="17">
         <v>114</v>
       </c>
@@ -4957,7 +4956,7 @@
       <c r="O115" s="17"/>
       <c r="P115" s="17"/>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="17">
         <v>115</v>
       </c>
@@ -4990,7 +4989,7 @@
       <c r="O116" s="17"/>
       <c r="P116" s="17"/>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="17">
         <v>116</v>
       </c>
@@ -5023,7 +5022,7 @@
       <c r="O117" s="17"/>
       <c r="P117" s="17"/>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="17">
         <v>117</v>
       </c>
@@ -5056,7 +5055,7 @@
       <c r="O118" s="17"/>
       <c r="P118" s="17"/>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="17">
         <v>118</v>
       </c>
@@ -5089,7 +5088,7 @@
       <c r="O119" s="17"/>
       <c r="P119" s="17"/>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="17">
         <v>119</v>
       </c>
@@ -5122,7 +5121,7 @@
       <c r="O120" s="17"/>
       <c r="P120" s="17"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="17">
         <v>120</v>
       </c>
@@ -5155,7 +5154,7 @@
       <c r="O121" s="17"/>
       <c r="P121" s="17"/>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="17">
         <v>121</v>
       </c>
@@ -5188,7 +5187,7 @@
       <c r="O122" s="17"/>
       <c r="P122" s="17"/>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="17">
         <v>122</v>
       </c>
@@ -5221,7 +5220,7 @@
       <c r="O123" s="17"/>
       <c r="P123" s="17"/>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="17">
         <v>123</v>
       </c>
@@ -5254,7 +5253,7 @@
       <c r="O124" s="17"/>
       <c r="P124" s="17"/>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="17">
         <v>124</v>
       </c>
@@ -5287,7 +5286,7 @@
       <c r="O125" s="17"/>
       <c r="P125" s="17"/>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="17">
         <v>125</v>
       </c>
@@ -5320,7 +5319,7 @@
       <c r="O126" s="17"/>
       <c r="P126" s="17"/>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="17">
         <v>126</v>
       </c>
@@ -5353,7 +5352,7 @@
       <c r="O127" s="17"/>
       <c r="P127" s="17"/>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="17">
         <v>127</v>
       </c>
@@ -5386,7 +5385,7 @@
       <c r="O128" s="17"/>
       <c r="P128" s="17"/>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="17">
         <v>128</v>
       </c>
@@ -5419,7 +5418,7 @@
       <c r="O129" s="17"/>
       <c r="P129" s="17"/>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="17">
         <v>129</v>
       </c>
@@ -5452,7 +5451,7 @@
       <c r="O130" s="17"/>
       <c r="P130" s="17"/>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="17">
         <v>130</v>
       </c>
@@ -5485,7 +5484,7 @@
       <c r="O131" s="17"/>
       <c r="P131" s="17"/>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="17">
         <v>131</v>
       </c>
@@ -5518,7 +5517,7 @@
       <c r="O132" s="17"/>
       <c r="P132" s="17"/>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="17">
         <v>132</v>
       </c>
@@ -5551,7 +5550,7 @@
       <c r="O133" s="17"/>
       <c r="P133" s="17"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="17">
         <v>133</v>
       </c>
@@ -5584,7 +5583,7 @@
       <c r="O134" s="17"/>
       <c r="P134" s="17"/>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="17">
         <v>134</v>
       </c>
@@ -5617,7 +5616,7 @@
       <c r="O135" s="17"/>
       <c r="P135" s="17"/>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="17">
         <v>135</v>
       </c>
@@ -5650,7 +5649,7 @@
       <c r="O136" s="17"/>
       <c r="P136" s="17"/>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="17">
         <v>136</v>
       </c>
@@ -5683,7 +5682,7 @@
       <c r="O137" s="17"/>
       <c r="P137" s="17"/>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="17">
         <v>137</v>
       </c>
@@ -5716,7 +5715,7 @@
       <c r="O138" s="17"/>
       <c r="P138" s="17"/>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="17">
         <v>138</v>
       </c>
@@ -5749,7 +5748,7 @@
       <c r="O139" s="17"/>
       <c r="P139" s="17"/>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="17">
         <v>139</v>
       </c>
@@ -5782,7 +5781,7 @@
       <c r="O140" s="17"/>
       <c r="P140" s="17"/>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="17">
         <v>140</v>
       </c>
@@ -5815,7 +5814,7 @@
       <c r="O141" s="17"/>
       <c r="P141" s="17"/>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="17">
         <v>141</v>
       </c>
@@ -5848,7 +5847,7 @@
       <c r="O142" s="17"/>
       <c r="P142" s="17"/>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="17">
         <v>142</v>
       </c>
@@ -5881,7 +5880,7 @@
       <c r="O143" s="17"/>
       <c r="P143" s="17"/>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="17">
         <v>143</v>
       </c>
@@ -5914,7 +5913,7 @@
       <c r="O144" s="17"/>
       <c r="P144" s="17"/>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="17">
         <v>144</v>
       </c>
@@ -5947,7 +5946,7 @@
       <c r="O145" s="17"/>
       <c r="P145" s="17"/>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="17">
         <v>145</v>
       </c>
@@ -5980,7 +5979,7 @@
       <c r="O146" s="17"/>
       <c r="P146" s="17"/>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="17">
         <v>146</v>
       </c>
@@ -6013,7 +6012,7 @@
       <c r="O147" s="17"/>
       <c r="P147" s="17"/>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="17">
         <v>147</v>
       </c>
@@ -6046,7 +6045,7 @@
       <c r="O148" s="17"/>
       <c r="P148" s="17"/>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="17">
         <v>148</v>
       </c>
@@ -6079,7 +6078,7 @@
       <c r="O149" s="17"/>
       <c r="P149" s="17"/>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="17">
         <v>149</v>
       </c>
@@ -6112,7 +6111,7 @@
       <c r="O150" s="17"/>
       <c r="P150" s="17"/>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="17">
         <v>150</v>
       </c>
@@ -6145,7 +6144,7 @@
       <c r="O151" s="17"/>
       <c r="P151" s="17"/>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="17">
         <v>151</v>
       </c>
@@ -6178,7 +6177,7 @@
       <c r="O152" s="17"/>
       <c r="P152" s="17"/>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="17">
         <v>152</v>
       </c>
@@ -6213,7 +6212,7 @@
       <c r="O153" s="17"/>
       <c r="P153" s="17"/>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="17">
         <v>153</v>
       </c>
@@ -6248,7 +6247,7 @@
       <c r="O154" s="17"/>
       <c r="P154" s="17"/>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="17">
         <v>154</v>
       </c>
@@ -6283,7 +6282,7 @@
       <c r="O155" s="17"/>
       <c r="P155" s="17"/>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="17">
         <v>155</v>
       </c>
@@ -6318,7 +6317,7 @@
       <c r="O156" s="17"/>
       <c r="P156" s="17"/>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="17">
         <v>156</v>
       </c>
@@ -6353,7 +6352,7 @@
       <c r="O157" s="17"/>
       <c r="P157" s="17"/>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="17">
         <v>157</v>
       </c>
@@ -6386,7 +6385,7 @@
       <c r="O158" s="17"/>
       <c r="P158" s="17"/>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="17">
         <v>158</v>
       </c>
@@ -6419,7 +6418,7 @@
       <c r="O159" s="17"/>
       <c r="P159" s="17"/>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="17">
         <v>159</v>
       </c>
@@ -6452,7 +6451,7 @@
       <c r="O160" s="17"/>
       <c r="P160" s="17"/>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="17">
         <v>160</v>
       </c>
@@ -6485,7 +6484,7 @@
       <c r="O161" s="17"/>
       <c r="P161" s="17"/>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="17">
         <v>161</v>
       </c>
@@ -6518,7 +6517,7 @@
       <c r="O162" s="17"/>
       <c r="P162" s="17"/>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="17">
         <v>162</v>
       </c>
@@ -6551,7 +6550,7 @@
       <c r="O163" s="17"/>
       <c r="P163" s="17"/>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="17">
         <v>163</v>
       </c>
@@ -6584,7 +6583,7 @@
       <c r="O164" s="17"/>
       <c r="P164" s="17"/>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="17">
         <v>164</v>
       </c>
@@ -6617,7 +6616,7 @@
       <c r="O165" s="17"/>
       <c r="P165" s="17"/>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="17">
         <v>165</v>
       </c>
@@ -6650,7 +6649,7 @@
       <c r="O166" s="17"/>
       <c r="P166" s="17"/>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="17">
         <v>166</v>
       </c>
@@ -6683,7 +6682,7 @@
       <c r="O167" s="17"/>
       <c r="P167" s="17"/>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="17">
         <v>167</v>
       </c>
@@ -6716,7 +6715,7 @@
       <c r="O168" s="17"/>
       <c r="P168" s="17"/>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="17">
         <v>168</v>
       </c>
@@ -6749,7 +6748,7 @@
       <c r="O169" s="17"/>
       <c r="P169" s="17"/>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="17">
         <v>169</v>
       </c>
@@ -6782,7 +6781,7 @@
       <c r="O170" s="17"/>
       <c r="P170" s="17"/>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="17">
         <v>170</v>
       </c>
@@ -6815,7 +6814,7 @@
       <c r="O171" s="17"/>
       <c r="P171" s="17"/>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="17">
         <v>171</v>
       </c>
@@ -6848,7 +6847,7 @@
       <c r="O172" s="17"/>
       <c r="P172" s="17"/>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="17">
         <v>172</v>
       </c>
@@ -6881,7 +6880,7 @@
       <c r="O173" s="17"/>
       <c r="P173" s="17"/>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="17">
         <v>173</v>
       </c>
@@ -6914,7 +6913,7 @@
       <c r="O174" s="17"/>
       <c r="P174" s="17"/>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="17">
         <v>174</v>
       </c>
@@ -6947,7 +6946,7 @@
       <c r="O175" s="17"/>
       <c r="P175" s="17"/>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="17">
         <v>175</v>
       </c>
@@ -6980,7 +6979,7 @@
       <c r="O176" s="17"/>
       <c r="P176" s="17"/>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="17">
         <v>176</v>
       </c>
@@ -7013,7 +7012,7 @@
       <c r="O177" s="17"/>
       <c r="P177" s="17"/>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="17">
         <v>177</v>
       </c>
@@ -7046,7 +7045,7 @@
       <c r="O178" s="17"/>
       <c r="P178" s="17"/>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="17">
         <v>178</v>
       </c>
@@ -7079,7 +7078,7 @@
       <c r="O179" s="17"/>
       <c r="P179" s="17"/>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="17">
         <v>179</v>
       </c>
@@ -7112,7 +7111,7 @@
       <c r="O180" s="17"/>
       <c r="P180" s="17"/>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="17">
         <v>180</v>
       </c>
@@ -7145,7 +7144,7 @@
       <c r="O181" s="17"/>
       <c r="P181" s="17"/>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="17">
         <v>181</v>
       </c>
@@ -7179,13 +7178,7 @@
       <c r="P182" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P182" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Manipulación de mercancía"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P182" xr:uid="{339774BC-59A6-4A79-9C09-252985CA5580}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="19" orientation="portrait" r:id="rId1"/>
 </worksheet>
